--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N23_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.47489552104338</v>
+        <v>3.16467052216955</v>
       </c>
       <c r="D2" t="n">
-        <v>19.70462870216664</v>
+        <v>3.20200216410208</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
